--- a/output/2026-10-04_16_Malesia_Sabah_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-10-04_16_Malesia_Sabah_Componentistica_Ventilazione_industriale.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Verificato via sito ufficiale (pagina contatti): indirizzo CL.015134282 Jalan Saga Off Mile 4.5 Jalan Tuaran Likas; telefono ed email confermati corrispondenti alla lista grezza.</t>
+          <t>Verificato via sito ufficiale (pagina contatti): indirizzo CL.015134282 Jalan Saga Off Mile 4.5 Jalan Tuaran Likas; telefono ed email confermati corrispondenti alla lista grezza. [DUPLICATO — vedi anche: 2026-10-04_11_Malesia_Sarawak_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Verificato via sito ufficiale (pagina contatti): Lot 7&amp;8 Block 7 Bandar Indah Mile 4 North Road Sandakan; telefono ed email confermati.</t>
+          <t>Verificato via sito ufficiale (pagina contatti): Lot 7&amp;8 Block 7 Bandar Indah Mile 4 North Road Sandakan; telefono ed email confermati. [DUPLICATO — vedi anche: 2026-10-04_11_Malesia_Sarawak_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Verificato via sito ufficiale (pagina contatti): 2140 Jalan Habib Hussin Tawau; telefono ed email confermati.</t>
+          <t>Verificato via sito ufficiale (pagina contatti): 2140 Jalan Habib Hussin Tawau; telefono ed email confermati. [DUPLICATO — vedi anche: 2026-10-04_11_Malesia_Sarawak_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Verificato via sito ufficiale (pagina contatti): A376 Lot 1 Batu 1 Jalan Tengah Nipah Lahad Datu; telefono ed email confermati.</t>
+          <t>Verificato via sito ufficiale (pagina contatti): A376 Lot 1 Batu 1 Jalan Tengah Nipah Lahad Datu; telefono ed email confermati. [DUPLICATO — vedi anche: 2026-10-04_11_Malesia_Sarawak_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -632,7 +632,6 @@
           <t>Alliance Bearings Sdn Bhd (outlet Kota Kinabalu)</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Kota Kinabalu, Sabah</t>
@@ -643,8 +642,6 @@
           <t>Distributore autorizzato SKF: cuscinetti, tenute/seals, lubrificanti - componenti per ventole/motori di aspirazione industriale</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Esistenza aziendale e presenza di un outlet a Kota Kinabalu confermate via ricerca web (azienda storica, dal 1986, con 6 outlet in Borneo inclusa KK). Indirizzo/telefono/email specifici del punto vendita KK non reperiti con fonte affidabile: lasciati vuoti invece di indovinare.</t>
@@ -694,7 +691,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -731,7 +728,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Verificato via pagina contatti ufficiale sito mhsc.com.my: Shoplot No.8 HSK Industrial Center Jalan Bundusan 89500 Penampang Sabah. Seconda filiale Sabah oltre a Sepangar (sede legale/HQ risulta a Miri, Sarawak).</t>
+          <t>Verificato via pagina contatti ufficiale sito mhsc.com.my: Shoplot No.8 HSK Industrial Center Jalan Bundusan 89500 Penampang Sabah. Seconda filiale Sabah oltre a Sepangar (sede legale/HQ risulta a Miri, Sarawak). [DUPLICATO — vedi anche: 2026-10-04_16_Malesia_Sabah_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
